--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561273187</v>
+        <v>46157.93066987085</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93066987085</v>
+        <v>46157.93151048806</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93151048806</v>
+        <v>46157.93392924067</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93392924067</v>
+        <v>46157.93706734775</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93706734775</v>
+        <v>46158.28210021013</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210021013</v>
+        <v>46158.29664813287</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29664813287</v>
+        <v>46158.29803657955</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29803657955</v>
+        <v>46158.33380696644</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33380696644</v>
+        <v>46158.36846861104</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Административнное исковое заявление и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36846861104</v>
+        <v>46158.37280960191</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
